--- a/docs/oc-top-proveedores/mobiliario-general-escolar-y-clinico.xlsx
+++ b/docs/oc-top-proveedores/mobiliario-general-escolar-y-clinico.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mobiliario-gener top prov" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="mobiliario-gener top prov" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -20378,7 +20378,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20576,7 +20576,7 @@
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -20992,7 +20992,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -23798,7 +23798,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -24835,7 +24835,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -25216,7 +25216,7 @@
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
@@ -25266,7 +25266,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25388,7 +25388,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -26364,7 +26364,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -27584,7 +27584,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -28133,7 +28133,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28438,7 +28438,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28804,7 +28804,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -29292,7 +29292,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29902,7 +29902,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -30207,7 +30207,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30268,7 +30268,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30329,7 +30329,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -31305,7 +31305,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31488,7 +31488,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31610,7 +31610,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31915,7 +31915,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -32037,7 +32037,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32464,7 +32464,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32830,7 +32830,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32891,7 +32891,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -33074,7 +33074,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -33196,7 +33196,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -33989,7 +33989,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34233,7 +34233,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34294,7 +34294,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34416,7 +34416,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34477,7 +34477,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -34538,7 +34538,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34599,7 +34599,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34721,7 +34721,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -34782,7 +34782,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -34843,7 +34843,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -34904,7 +34904,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -34965,7 +34965,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35026,7 +35026,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35087,7 +35087,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35148,7 +35148,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35209,7 +35209,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35270,7 +35270,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35331,7 +35331,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35392,7 +35392,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35453,7 +35453,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -35514,7 +35514,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35575,7 +35575,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -35636,7 +35636,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35697,7 +35697,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35758,7 +35758,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -35880,7 +35880,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -35941,7 +35941,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -36002,7 +36002,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36063,7 +36063,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36124,7 +36124,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36185,7 +36185,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36307,7 +36307,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36368,7 +36368,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -36429,7 +36429,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -36490,7 +36490,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36551,7 +36551,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -36612,7 +36612,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -36673,7 +36673,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -36734,7 +36734,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36795,7 +36795,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -36856,7 +36856,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
